--- a/表格模版/罗马尼亚鹏城.xlsx
+++ b/表格模版/罗马尼亚鹏城.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27420" windowHeight="11080"/>
+    <workbookView windowWidth="26040" windowHeight="11720"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -333,7 +333,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
   <si>
     <t>渠道服务（必填）*</t>
   </si>
@@ -345,6 +345,9 @@
 （在海外仓地址库复制）</t>
   </si>
   <si>
+    <t>DC2-087151</t>
+  </si>
+  <si>
     <t>带电（必填）*</t>
   </si>
   <si>
@@ -354,18 +357,27 @@
     <t>收件人姓名（必填）*</t>
   </si>
   <si>
+    <t>Receptie DC2</t>
+  </si>
+  <si>
     <t>带磁（必填）*</t>
   </si>
   <si>
     <t>收件人公司</t>
   </si>
   <si>
+    <t>eMAG</t>
+  </si>
+  <si>
     <t>粉末（必填)*</t>
   </si>
   <si>
     <t>收件人地址一（必填）*</t>
   </si>
   <si>
+    <t>Strada Ciorogarla 214,Rampa S35</t>
+  </si>
+  <si>
     <t>液体(必填）*</t>
   </si>
   <si>
@@ -388,6 +400,9 @@
   </si>
   <si>
     <t>收件人城市（必填）*</t>
+  </si>
+  <si>
+    <t> comuna Joita sat Bacu</t>
   </si>
   <si>
     <r>
@@ -413,6 +428,9 @@
     <t>收件人省份/州（必填）*</t>
   </si>
   <si>
+    <t>Giurgiu</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -460,6 +478,9 @@
 (二字代码)（必填）*</t>
   </si>
   <si>
+    <t>RO</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -481,6 +502,9 @@
   </si>
   <si>
     <t>收件人电话</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0720335869  </t>
   </si>
   <si>
     <r>
@@ -2187,14 +2211,16 @@
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="9"/>
+      <c r="B2" s="9" t="s">
+        <v>3</v>
+      </c>
       <c r="C2" s="10"/>
       <c r="D2" s="7"/>
       <c r="E2" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
@@ -2215,16 +2241,18 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="C3" s="13"/>
       <c r="D3" s="7"/>
       <c r="E3" s="11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="22"/>
@@ -2245,16 +2273,18 @@
     </row>
     <row r="4" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A4" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>10</v>
+      </c>
       <c r="C4" s="13"/>
       <c r="D4" s="7"/>
       <c r="E4" s="11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
@@ -2275,16 +2305,18 @@
     </row>
     <row r="5" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A5" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>13</v>
+      </c>
       <c r="C5" s="13"/>
       <c r="D5" s="7"/>
       <c r="E5" s="11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
@@ -2305,16 +2337,16 @@
     </row>
     <row r="6" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A6" s="14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="13"/>
       <c r="D6" s="7"/>
       <c r="E6" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
@@ -2335,16 +2367,16 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A7" s="14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="13"/>
       <c r="D7" s="7"/>
       <c r="E7" s="11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
@@ -2365,13 +2397,15 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="17" spans="1:22">
       <c r="A8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="C8" s="13"/>
       <c r="D8" s="7"/>
       <c r="E8" s="23" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F8" s="14"/>
       <c r="G8" s="22"/>
@@ -2393,13 +2427,15 @@
     </row>
     <row r="9" s="1" customFormat="1" ht="17" spans="1:22">
       <c r="A9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="C9" s="13"/>
       <c r="D9" s="7"/>
       <c r="E9" s="23" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="22"/>
@@ -2421,13 +2457,15 @@
     </row>
     <row r="10" s="1" customFormat="1" ht="17" spans="1:22">
       <c r="A10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="12"/>
+        <v>27</v>
+      </c>
+      <c r="B10" s="12">
+        <v>87151</v>
+      </c>
       <c r="C10" s="13"/>
       <c r="D10" s="7"/>
       <c r="E10" s="23" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="22"/>
@@ -2449,13 +2487,15 @@
     </row>
     <row r="11" s="1" customFormat="1" ht="34" spans="1:22">
       <c r="A11" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="C11" s="13"/>
       <c r="D11" s="7"/>
       <c r="E11" s="23" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F11" s="14"/>
       <c r="G11" s="22"/>
@@ -2477,13 +2517,15 @@
     </row>
     <row r="12" s="1" customFormat="1" ht="17" spans="1:22">
       <c r="A12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>33</v>
+      </c>
       <c r="C12" s="13"/>
       <c r="D12" s="7"/>
       <c r="E12" s="23" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F12" s="14"/>
       <c r="G12" s="22"/>
@@ -2505,13 +2547,13 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="17" spans="1:22">
       <c r="A13" s="12" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="13"/>
       <c r="D13" s="16"/>
       <c r="E13" s="23" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F13" s="14"/>
       <c r="G13" s="22"/>
@@ -2533,15 +2575,15 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="51" spans="1:22">
       <c r="A14" s="17" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="7"/>
       <c r="E14" s="14" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="22"/>
@@ -2563,15 +2605,15 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A15" s="18" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="14" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13"/>
@@ -2593,7 +2635,7 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A16" s="18" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="13"/>
@@ -2619,10 +2661,10 @@
     </row>
     <row r="17" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A17" s="18" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="7"/>
@@ -2671,70 +2713,70 @@
     </row>
     <row r="19" s="2" customFormat="1" ht="49.95" customHeight="1" spans="1:22">
       <c r="A19" s="19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K19" s="28" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L19" s="28" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N19" s="28" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="O19" s="19" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="P19" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="Q19" s="19" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="R19" s="19" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="S19" s="31" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="T19" s="32" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="U19" s="36" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="V19" s="37" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="48" customHeight="1" spans="1:21">

--- a/表格模版/罗马尼亚鹏城.xlsx
+++ b/表格模版/罗马尼亚鹏城.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26040" windowHeight="11720"/>
+    <workbookView windowWidth="26260" windowHeight="13900"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -333,9 +333,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
   <si>
     <t>渠道服务（必填）*</t>
+  </si>
+  <si>
+    <t>罗马尼亚FBE铁卡联运</t>
   </si>
   <si>
     <t>箱数（必填）*</t>
@@ -2183,11 +2186,13 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
       <c r="E1" s="11" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="12"/>
       <c r="G1" s="22"/>
@@ -2209,18 +2214,18 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="51" spans="1:22">
       <c r="A2" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="7"/>
       <c r="E2" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
@@ -2241,18 +2246,18 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A3" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="7"/>
       <c r="E3" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="22"/>
@@ -2273,18 +2278,18 @@
     </row>
     <row r="4" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A4" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="7"/>
       <c r="E4" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
@@ -2305,18 +2310,18 @@
     </row>
     <row r="5" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A5" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="7"/>
       <c r="E5" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
@@ -2337,16 +2342,16 @@
     </row>
     <row r="6" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A6" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="13"/>
       <c r="D6" s="7"/>
       <c r="E6" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
@@ -2367,16 +2372,16 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A7" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="13"/>
       <c r="D7" s="7"/>
       <c r="E7" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
@@ -2397,15 +2402,15 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="17" spans="1:22">
       <c r="A8" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="7"/>
       <c r="E8" s="23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="14"/>
       <c r="G8" s="22"/>
@@ -2427,15 +2432,15 @@
     </row>
     <row r="9" s="1" customFormat="1" ht="17" spans="1:22">
       <c r="A9" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="7"/>
       <c r="E9" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="22"/>
@@ -2457,7 +2462,7 @@
     </row>
     <row r="10" s="1" customFormat="1" ht="17" spans="1:22">
       <c r="A10" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="12">
         <v>87151</v>
@@ -2465,7 +2470,7 @@
       <c r="C10" s="13"/>
       <c r="D10" s="7"/>
       <c r="E10" s="23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="22"/>
@@ -2487,15 +2492,15 @@
     </row>
     <row r="11" s="1" customFormat="1" ht="34" spans="1:22">
       <c r="A11" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="7"/>
       <c r="E11" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" s="14"/>
       <c r="G11" s="22"/>
@@ -2517,15 +2522,15 @@
     </row>
     <row r="12" s="1" customFormat="1" ht="17" spans="1:22">
       <c r="A12" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="7"/>
       <c r="E12" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" s="14"/>
       <c r="G12" s="22"/>
@@ -2547,13 +2552,13 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="17" spans="1:22">
       <c r="A13" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="13"/>
       <c r="D13" s="16"/>
       <c r="E13" s="23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" s="14"/>
       <c r="G13" s="22"/>
@@ -2575,15 +2580,15 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="51" spans="1:22">
       <c r="A14" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="7"/>
       <c r="E14" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="22"/>
@@ -2605,15 +2610,15 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A15" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13"/>
@@ -2635,7 +2640,7 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A16" s="18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="13"/>
@@ -2661,10 +2666,10 @@
     </row>
     <row r="17" s="1" customFormat="1" ht="16.8" spans="1:22">
       <c r="A17" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="7"/>
@@ -2713,70 +2718,70 @@
     </row>
     <row r="19" s="2" customFormat="1" ht="49.95" customHeight="1" spans="1:22">
       <c r="A19" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K19" s="28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L19" s="28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N19" s="28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O19" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P19" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q19" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R19" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S19" s="31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T19" s="32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U19" s="36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V19" s="37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="48" customHeight="1" spans="1:21">

--- a/表格模版/罗马尼亚鹏城.xlsx
+++ b/表格模版/罗马尼亚鹏城.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27180" windowHeight="13740"/>
+    <workbookView windowWidth="22100" windowHeight="9940"/>
   </bookViews>
   <sheets>
     <sheet name="发票箱单" sheetId="1" r:id="rId1"/>
@@ -337,7 +337,7 @@
     <t>渠道服务（必填）*</t>
   </si>
   <si>
-    <t>罗马尼亚空派经济带电</t>
+    <t>罗马尼亚空派经济普货</t>
   </si>
   <si>
     <t>箱数（必填）*</t>
@@ -11504,7 +11504,7 @@
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
-      <formula1>渠道服务!$A$2:$A$109</formula1>
+      <formula1>渠道服务!$A$1:$A$109</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5:S5 B15 F2:G5">
       <formula1>"是,否"</formula1>
